--- a/artfynd/A 52117-2022 artfynd.xlsx
+++ b/artfynd/A 52117-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 52117-2022 artfynd.xlsx
+++ b/artfynd/A 52117-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,48 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>107793694</v>
+        <v>107793680</v>
       </c>
       <c r="B2" t="n">
-        <v>43464</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79148</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>101735</v>
+        <v>924</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Lecanora glabrata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Ach.) Malme</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -724,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>381716.3383272865</v>
+        <v>381717</v>
       </c>
       <c r="R2" t="n">
-        <v>6310539.546909978</v>
+        <v>6310541</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -757,19 +746,9 @@
           <t>2023-04-03</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-04-03</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,42 +776,38 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>107793680</v>
+        <v>107793471</v>
       </c>
       <c r="B3" t="n">
-        <v>77323</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96447</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>924</v>
+        <v>1080</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bokkantlav</t>
+          <t>Bokfjädermossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lecanora glabrata</t>
+          <t>Neckera pumila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Malme</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -840,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>381717.4627538015</v>
+        <v>381785</v>
       </c>
       <c r="R3" t="n">
-        <v>6310540.607035235</v>
+        <v>6310540</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -873,19 +848,9 @@
           <t>2023-04-03</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-04-03</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,37 +878,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>107793558</v>
+        <v>107793683</v>
       </c>
       <c r="B4" t="n">
-        <v>77756</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>77726</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6459</v>
+        <v>1342</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -956,10 +916,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>381757.1043570921</v>
+        <v>381716</v>
       </c>
       <c r="R4" t="n">
-        <v>6310549.30900655</v>
+        <v>6310540</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -989,19 +949,9 @@
           <t>2023-04-03</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-04-03</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,37 +979,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>107793683</v>
+        <v>107793558</v>
       </c>
       <c r="B5" t="n">
-        <v>75910</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79583</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1342</v>
+        <v>6459</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1072,10 +1017,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>381716.3383272865</v>
+        <v>381758</v>
       </c>
       <c r="R5" t="n">
-        <v>6310539.546909978</v>
+        <v>6310549</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1105,19 +1050,9 @@
           <t>2023-04-03</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-04-03</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,6 +1077,113 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>107793694</v>
+      </c>
+      <c r="B6" t="n">
+        <v>44177</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>101735</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Jättesvampmal</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Scardia boletella</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Hinnakullsberg, Hl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>381716</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6310540</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Hylte</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Torup</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-04-03</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-04-03</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Monica Mathiasson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Monica Mathiasson, Sindy Gullberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 52117-2022 artfynd.xlsx
+++ b/artfynd/A 52117-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107793680</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107793471</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -976,6 +991,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107793683</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1077,6 +1097,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107793558</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1184,8 +1209,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107793694</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>